--- a/GET_WEATHER_RESULTS_TripId_2_Milan.xlsx
+++ b/GET_WEATHER_RESULTS_TripId_2_Milan.xlsx
@@ -31,13 +31,13 @@
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>5.1°C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The forecast for Milan shows an average temperature of 5.1°C with a rain probability of 0%.</x:t>
+    <x:t>29.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The forecast for Milan during 10 August 2026 - 15 August 2026 shows an average temperature of 29.7°C with a rain probability of 17%.</x:t>
   </x:si>
 </x:sst>
 </file>
